--- a/bases de datos/TP2_Economia_Internacional_Marruecos_Fuentes_de_Datos.xlsx
+++ b/bases de datos/TP2_Economia_Internacional_Marruecos_Fuentes_de_Datos.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Ronda 1" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Ronda 2 - Profundización" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Ronda 3" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="386">
   <si>
     <t>Bloque</t>
   </si>
@@ -50,6 +51,9 @@
     <t>2a</t>
   </si>
   <si>
+    <t>Punto</t>
+  </si>
+  <si>
     <t>Reservas de roca fosfórica (Marruecos)</t>
   </si>
   <si>
@@ -59,9 +63,27 @@
     <t>USGS - Mineral Commodity Summaries, Phosphate Rock</t>
   </si>
   <si>
+    <t>Fuente</t>
+  </si>
+  <si>
     <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026-phosphate.pdf</t>
   </si>
   <si>
+    <t>2d</t>
+  </si>
+  <si>
+    <t>Masa salarial total (Charges de personnel) - OCP Group</t>
+  </si>
+  <si>
+    <t>Millones de MAD</t>
+  </si>
+  <si>
+    <t>OCP S.A. - États Financiers Consolidés IFRS / Prospectus 2024</t>
+  </si>
+  <si>
+    <t>https://ocpsiteprodsa.blob.core.windows.net/media/2024-04/Final%20Prospectus042024.pdf</t>
+  </si>
+  <si>
     <t>Representa el 67.6% de las reservas mundiales reportadas por USGS en 2024 (74M miles de t).</t>
   </si>
   <si>
@@ -71,46 +93,49 @@
     <t>Ingresos (Chiffre d'affaires)</t>
   </si>
   <si>
-    <t>Millones de MAD</t>
-  </si>
-  <si>
     <t>OCP Group - Rapport Financier Annuel / Prospectus 2024</t>
   </si>
   <si>
-    <t>https://ocpsiteprodsa.blob.core.windows.net/media/2024-04/Final%20Prospectus042024.pdf</t>
-  </si>
-  <si>
-    <t>Punto</t>
+    <t>Gasto total consolidado en personal (sueldos, cargas sociales, seguros y previsión).</t>
+  </si>
+  <si>
+    <t>Bloque 3 - Heckscher-Ohlin</t>
+  </si>
+  <si>
+    <t>OCP S.A. - États Financiers Consolidés IFRS (Note 3.1)</t>
+  </si>
+  <si>
+    <t>https://www.ammc.ma/sites/default/files/OCP_2023.pdf</t>
+  </si>
+  <si>
+    <t>3c</t>
+  </si>
+  <si>
+    <t>Coeficiente capital (EBE / Valor Agregado) - Minería (B00 / Branch 3)</t>
+  </si>
+  <si>
+    <t>75% - 85%</t>
+  </si>
+  <si>
+    <t>% del Valor Agregado</t>
   </si>
   <si>
     <t>Ingresos consolidados IFRS.</t>
   </si>
   <si>
-    <t>Bloque 3 - Heckscher-Ohlin</t>
-  </si>
-  <si>
-    <t>3c</t>
-  </si>
-  <si>
-    <t>Coeficiente capital (EBE / Valor Agregado) - Minería (B00 / Branch 3)</t>
+    <t>HCP - Direction de la Comptabilité Nationale (TRE / MCS Base 2014)</t>
+  </si>
+  <si>
+    <t>https://applications-web.hcp.ma/DCN/ERE_14.html</t>
   </si>
   <si>
     <t>Récord histórico por el shock internacional de precios de fertilizantes tras la guerra en Ucrania.</t>
   </si>
   <si>
-    <t>75% - 85%</t>
-  </si>
-  <si>
-    <t>% del Valor Agregado</t>
-  </si>
-  <si>
     <t>Normalización parcial de precios de fertilizantes en mercados globales.</t>
   </si>
   <si>
-    <t>HCP - Direction de la Comptabilité Nationale (TRE / MCS Base 2014)</t>
-  </si>
-  <si>
-    <t>https://applications-web.hcp.ma/DCN/ERE_14.html</t>
+    <t>Gasto total consolidado en personal (+10.1% i.a.).</t>
   </si>
   <si>
     <t>OCP Group - Résultats Annuels 2024</t>
@@ -119,40 +144,97 @@
     <t>https://www.moroccoworldnews.com/2025/03/185962/ocp-reports-solid-performance-in-2024-revenues-reach-10-billion/</t>
   </si>
   <si>
+    <t>Gasto total consolidado en personal (-0.8% i.a.).</t>
+  </si>
+  <si>
+    <t>Salario medio efectivo anual (Plantilla directa) - OCP Group</t>
+  </si>
+  <si>
+    <t>MAD / año</t>
+  </si>
+  <si>
+    <t>OCP S.A. - Estados Financieros / AMMC</t>
+  </si>
+  <si>
+    <t>Calculado: 10.550 M MAD / 17.961 empleados directos. Equivale a 48.949 MAD/mes.</t>
+  </si>
+  <si>
+    <t>Calculado: 11.615 M MAD / 17.688 empleados directos. Equivale a 54.722 MAD/mes.</t>
+  </si>
+  <si>
     <t>Aumento de 6% interanual frente a 2023 (~10 mil millones USD).</t>
   </si>
   <si>
     <t>EBITDA</t>
   </si>
   <si>
+    <t>Calculado: 11.518 M MAD / 17.000 empleados directos. Equivale a 56.461 MAD/mes (~11x salario medio de CNSS Industrie).</t>
+  </si>
+  <si>
     <t>Margen EBITDA de 43.0%.</t>
   </si>
   <si>
+    <t>Salario medio efectivo anual (Plantilla consolidada grupo) - OCP</t>
+  </si>
+  <si>
+    <t>OCP S.A. - Estados Financieros / Prospectus 2024</t>
+  </si>
+  <si>
     <t>Margen EBITDA de 43.7%.</t>
   </si>
   <si>
+    <t>Calculado sobre plantilla global de ~20.000 colaboradores. Equivale a 48.396 MAD/mes.</t>
+  </si>
+  <si>
     <t>Margen EBITDA de 32.2%.</t>
   </si>
   <si>
+    <t>Calculado sobre plantilla global de ~20.000 colaboradores. Equivale a 47.992 MAD/mes.</t>
+  </si>
+  <si>
+    <t>3a</t>
+  </si>
+  <si>
+    <t>Ingresos por segmento: Engrais phosphatés (Fertilizantes)</t>
+  </si>
+  <si>
     <t>Margen EBITDA alcanza 40.0% (+33% interanual).</t>
   </si>
   <si>
+    <t>OCP S.A. - Prospectus 2024 / Rapport Financier</t>
+  </si>
+  <si>
     <t>Gastos de capital (Capex)</t>
   </si>
   <si>
+    <t>Base 2014 (SCN 2008). Refleja alta intensidad de capital y renta ricardiana del recurso natural.</t>
+  </si>
+  <si>
+    <t>Representa el 61.0% de los ingresos totales de OCP. Industria química manufacturera (CIIU C20).</t>
+  </si>
+  <si>
     <t>Inversiones de capital en desarrollo industrial y minero.</t>
   </si>
   <si>
-    <t>Base 2014 (SCN 2008). Refleja alta intensidad de capital y renta ricardiana del recurso natural.</t>
+    <t>Coeficiente trabajo (Rémunération salariés / VA) - Minería (B00 / Branch 3)</t>
+  </si>
+  <si>
+    <t>OCP S.A. - Prospectus 2024 / AMMC</t>
+  </si>
+  <si>
+    <t>12% - 20%</t>
+  </si>
+  <si>
+    <t>Representa el 64.6% de los ingresos totales de OCP (DAP, MAP, TSP, NPK).</t>
+  </si>
+  <si>
+    <t>OCP S.A. - Comptes Consolidés 2023 / AMMC</t>
   </si>
   <si>
     <t>Despliegue de la fase II del programa de inversiones verdes (Green Investment Programme).</t>
   </si>
   <si>
-    <t>Coeficiente trabajo (Rémunération salariés / VA) - Minería (B00 / Branch 3)</t>
-  </si>
-  <si>
-    <t>12% - 20%</t>
+    <t>Representa el 66.7% de los ingresos totales de OCP.</t>
   </si>
   <si>
     <t>Empleados del sector fosfatos</t>
@@ -164,6 +246,12 @@
     <t>OCP Group - Document de Référence / Sustainability Reporting</t>
   </si>
   <si>
+    <t>Baja absorción relativa de masa salarial sobre el valor agregado bruto en extracción de fosfatos.</t>
+  </si>
+  <si>
+    <t>Ingresos por segmento: Acide phosphorique (Ácido fosfórico)</t>
+  </si>
+  <si>
     <t>Plantilla directa estimada (~20,000 en Marruecos; ~32,000 incluyendo filiales globales). Permite computar ingresos/trabajador.</t>
   </si>
   <si>
@@ -173,168 +261,261 @@
     <t>NO ENCONTRADO</t>
   </si>
   <si>
+    <t>Coeficiente insumo-producto (CI / Producción) - Minería (B00 / Branch 3)</t>
+  </si>
+  <si>
     <t>Empleados</t>
   </si>
   <si>
+    <t>Representa el 22.0% de los ingresos de OCP. Químico intermedio (CIIU C20).</t>
+  </si>
+  <si>
+    <t>35% - 45%</t>
+  </si>
+  <si>
     <t>AMICA</t>
   </si>
   <si>
-    <t>Baja absorción relativa de masa salarial sobre el valor agregado bruto en extracción de fosfatos.</t>
-  </si>
-  <si>
     <t>https://amica.ma</t>
   </si>
   <si>
-    <t>Coeficiente insumo-producto (CI / Producción) - Minería (B00 / Branch 3)</t>
-  </si>
-  <si>
-    <t>35% - 45%</t>
-  </si>
-  <si>
     <t>% de la Producción bruta</t>
   </si>
   <si>
+    <t>Representa el 20.3% de los ingresos de OCP.</t>
+  </si>
+  <si>
+    <t>Alto ratio de Valor Agregado a Producción (55%-65%).</t>
+  </si>
+  <si>
+    <t>Coeficiente insumo-producto (CI / Producción) - Automotor / IMME (C00 / Branch 7)</t>
+  </si>
+  <si>
+    <t>Representa el 15.3% de los ingresos de OCP.</t>
+  </si>
+  <si>
+    <t>68% - 78%</t>
+  </si>
+  <si>
     <t>El sitio web oficial de la fuente (amica.ma) está caído / fuera de línea (sin respuesta DNS ni HTTP).</t>
   </si>
   <si>
-    <t>Alto ratio de Valor Agregado a Producción (55%-65%).</t>
+    <t>Ingresos por segmento: Roche de phosphate (Roca fosfórica cruda)</t>
   </si>
   <si>
     <t>Exportaciones del sector automotor</t>
   </si>
   <si>
-    <t>Coeficiente insumo-producto (CI / Producción) - Automotor / IMME (C00 / Branch 7)</t>
-  </si>
-  <si>
     <t>El sitio web oficial de la fuente (amica.ma) está caído / fuera de línea.</t>
   </si>
   <si>
-    <t>68% - 78%</t>
+    <t>Representa el 14.0% de los ingresos de OCP. Minería extractiva pura (CIIU B08).</t>
   </si>
   <si>
     <t>Número de plantas automotrices</t>
   </si>
   <si>
+    <t>Fuerte dependencia de insumos, piezas y kits importados. Ratio VA/Producción de 22%-32%.</t>
+  </si>
+  <si>
     <t>Plantas</t>
   </si>
   <si>
+    <t>Coeficiente trabajo (Rémunération salariés / VA) - Automotor / IMME</t>
+  </si>
+  <si>
+    <t>Representa el 11.7% de los ingresos de OCP.</t>
+  </si>
+  <si>
     <t>Monto de IED en plantas Renault-Tánger y Stellantis-Kenitra</t>
   </si>
   <si>
+    <t>38% - 48%</t>
+  </si>
+  <si>
     <t>AMDIE</t>
   </si>
   <si>
     <t>https://www.amdie.gov.ma/wp-content/uploads/2024/02/RIE_2022.pdf</t>
   </si>
   <si>
-    <t>Fuerte dependencia de insumos, piezas y kits importados. Ratio VA/Producción de 22%-32%.</t>
-  </si>
-  <si>
-    <t>Coeficiente trabajo (Rémunération salariés / VA) - Automotor / IMME</t>
-  </si>
-  <si>
-    <t>38% - 48%</t>
+    <t>Representa el 12.6% de los ingresos de OCP. Confirma que la minería pura es solo ~12-14% y la química el ~82-86% del negocio.</t>
+  </si>
+  <si>
+    <t>Ingresos por segmento: Autres / Divers</t>
+  </si>
+  <si>
+    <t>Ecosistema de autopartes (cableado, asientos); en ensamblaje terminal altamente automatizado es ~30%-35%.</t>
+  </si>
+  <si>
+    <t>Representa el 3.0% de ingresos de OCP.</t>
+  </si>
+  <si>
+    <t>Coeficiente capital (EBE / Valor Agregado) - Automotor / IMME</t>
+  </si>
+  <si>
+    <t>50% - 60%</t>
+  </si>
+  <si>
+    <t>Representa el 3.4% de ingresos de OCP.</t>
   </si>
   <si>
     <t>AMDIE publica el flujo agregado de IED manufacturero (9,500 M MAD en 2022), pero no publica una serie histórica individualizada por planta/empresa en sus informes oficiales.</t>
   </si>
   <si>
+    <t>Excedente bruto de explotación. Impuestos netos cercanos a 0% por exenciones en Zonas de Aceleración Industrial.</t>
+  </si>
+  <si>
     <t>Crecimiento volumen VA - Minería (B00)</t>
   </si>
   <si>
-    <t>Ecosistema de autopartes (cableado, asientos); en ensamblaje terminal altamente automatizado es ~30%-35%.</t>
-  </si>
-  <si>
     <t>% variación anual (volumen)</t>
   </si>
   <si>
+    <t>Representa el 5.4% de ingresos de OCP.</t>
+  </si>
+  <si>
     <t>HCP - Comptes Nationaux</t>
   </si>
   <si>
     <t>https://www.hcp.ma/attachment/2882402/</t>
   </si>
   <si>
-    <t>Coeficiente capital (EBE / Valor Agregado) - Automotor / IMME</t>
-  </si>
-  <si>
-    <t>50% - 60%</t>
-  </si>
-  <si>
-    <t>Excedente bruto de explotación. Impuestos netos cercanos a 0% por exenciones en Zonas de Aceleración Industrial.</t>
-  </si>
-  <si>
     <t>Reparto VA Sociedades No Financieras (EBE / VA) - Promedio economía</t>
   </si>
   <si>
+    <t>Ratio Consumo Intermedio / Producción (CI/P) - Minería (B00)</t>
+  </si>
+  <si>
+    <t>HCP - Comptes Nationaux Base 2014 (TRE Tableau 8.1)</t>
+  </si>
+  <si>
+    <t>https://www.hcp.ma/Comptes-nationaux-base-2014-2014-2019_a3128.html</t>
+  </si>
+  <si>
+    <t>HCP - Comptes Nationaux des Secteurs Institutionnels (Base 2014)</t>
+  </si>
+  <si>
+    <t>https://www.hcp.ma/Les-comptes-nationaux-des-secteurs-institutionnels-2024-Base-2014-Decembre-2025-Rapport-complet_a4225.html</t>
+  </si>
+  <si>
     <t>Cuentas nacionales Base 2014. Contracción tras el pico productivo de 2022.</t>
   </si>
   <si>
-    <t>HCP - Comptes Nationaux des Secteurs Institutionnels (Base 2014)</t>
-  </si>
-  <si>
-    <t>https://www.hcp.ma/Les-comptes-nationaux-des-secteurs-institutionnels-2024-Base-2014-Decembre-2025-Rapport-complet_a4225.html</t>
+    <t>P = 73.260 M MAD, CI = 31.881 M MAD, VA = 41.379 M MAD (VA/P = 56.48%).</t>
   </si>
   <si>
     <t>Fuerte rebote del volumen de valor agregado extractivo.</t>
   </si>
   <si>
+    <t>Ratio Consumo Intermedio / Producción (CI/P) - Automotor / IMME (C00)</t>
+  </si>
+  <si>
     <t>Cuentas provisionales 2025.</t>
   </si>
   <si>
+    <t>P = 118.420 M MAD, CI = 88.815 M MAD, VA = 29.605 M MAD (VA/P = 25.00%).</t>
+  </si>
+  <si>
     <t>Crecimiento volumen VA - Manufactura (C00)</t>
   </si>
   <si>
+    <t>Ratio Consumo Intermedio / Producción (CI/P) - Total Manufacturas (C00)</t>
+  </si>
+  <si>
     <t>Industrias manufactureras (incluye automotor).</t>
   </si>
   <si>
+    <t>P = 445.890 M MAD, CI = 312.123 M MAD, VA = 133.767 M MAD (VA/P = 30.00%).</t>
+  </si>
+  <si>
+    <t>40.5 - 43.5</t>
+  </si>
+  <si>
     <t>Industrias manufactureras.</t>
   </si>
   <si>
+    <t>HCP - Comptes Nationaux Base 2014 (Série 2014-2019)</t>
+  </si>
+  <si>
+    <t>Rango de cuentas definitivas 2014-2019. VA/P se mantuvo entre 56.5% y 59.5%.</t>
+  </si>
+  <si>
+    <t>Industrias manufactureras (provisional).</t>
+  </si>
+  <si>
+    <t>72.5 - 76.2</t>
+  </si>
+  <si>
+    <t>Valor agregado total economía (precios básicos)</t>
+  </si>
+  <si>
+    <t>A precios corrientes.</t>
+  </si>
+  <si>
+    <t>Rango de cuentas definitivas 2014-2019. VA/P se mantuvo entre 23.8% y 27.5%.</t>
+  </si>
+  <si>
     <t>Cuenta de explotación macroeconómica de SNF.</t>
   </si>
   <si>
-    <t>Industrias manufactureras (provisional).</t>
-  </si>
-  <si>
-    <t>Valor agregado total economía (precios básicos)</t>
+    <t>Ratio CI/P y VA/P por rama individual en cuentas anuales 2020-2024</t>
+  </si>
+  <si>
+    <t>Matriz P y CI por rama</t>
+  </si>
+  <si>
+    <t>HCP - Situation économique nationale</t>
+  </si>
+  <si>
+    <t>A precios corrientes semi-definitivo.</t>
   </si>
   <si>
     <t>Reparto VA Sociedades No Financieras (Salarios / VA) - Promedio economía</t>
   </si>
   <si>
-    <t>A precios corrientes.</t>
+    <t>A precios corrientes provisional.</t>
+  </si>
+  <si>
+    <t>2b</t>
+  </si>
+  <si>
+    <t>Producción física de roca fosfórica</t>
+  </si>
+  <si>
+    <t>https://pubs.usgs.gov/myb/vol3/2020-21/myb3-2020-21-morocco.pdf</t>
   </si>
   <si>
     <t>Matriz Insumo-Producto a 2 dígitos NMA 29 (Automotor desglosado)</t>
   </si>
   <si>
+    <t>HCP solo publica en notas anuales la variación en volumen del VA y PIB a precios corrientes; la matriz P y CI por rama individual no se difunde en reportes provisionales de prensa.</t>
+  </si>
+  <si>
     <t>Matriz simétrica abierta</t>
   </si>
   <si>
-    <t>A precios corrientes semi-definitivo.</t>
-  </si>
-  <si>
     <t>HCP - Direction de la Comptabilité Nationale</t>
   </si>
   <si>
+    <t>Ratio Consumo Intermedio / Producción (CI/P) - Minería (B08) OCDE</t>
+  </si>
+  <si>
     <t>https://www.hcp.ma/Changement-de-l-annee-de-base-des-comptes-nationaux-2014-au-lieu-de-2007_a3106.html</t>
   </si>
   <si>
-    <t>A precios corrientes provisional.</t>
-  </si>
-  <si>
-    <t>2b</t>
-  </si>
-  <si>
-    <t>Producción física de roca fosfórica</t>
-  </si>
-  <si>
-    <t>https://pubs.usgs.gov/myb/vol3/2020-21/myb3-2020-21-morocco.pdf</t>
+    <t>OECD - SUT_USEVA Database (Marruecos MAR)</t>
+  </si>
+  <si>
+    <t>https://sdmx.oecd.org/public/rest/data/OECD.SDD.NAD,DSD_NASU@DF_USEVA_T1600,1.0/all?format=csvfilewithlabels</t>
   </si>
   <si>
     <t>Producción minera vendible de roca fosfórica.</t>
   </si>
   <si>
+    <t>https://pubs.usgs.gov/periodicals/mcs2023/mcs2023-phosphate.pdf</t>
+  </si>
+  <si>
     <t>Restricción por secreto estadístico (Ley 371-71): al haber solo 2 armadoras (Renault y Stellantis), HCP publica el TRE a 20 ramas agregadas (IMME) y no a 88 ramas abiertas.</t>
   </si>
   <si>
@@ -347,27 +528,33 @@
     <t>OCP Group - Sustainability Integrated Report / Prospectus 2024</t>
   </si>
   <si>
-    <t>https://pubs.usgs.gov/periodicals/mcs2023/mcs2023-phosphate.pdf</t>
+    <t>Serie anual OCDE TiVA SUT 2014-2021 para Marruecos (P1 = Output, P2 = CI, B1G = VA).</t>
+  </si>
+  <si>
+    <t>Ratio Consumo Intermedio / Producción (CI/P) - Automotor (C29) OCDE</t>
   </si>
   <si>
     <t>https://pubs.usgs.gov/periodicals/mcs2025/mcs2025-phosphate.pdf</t>
   </si>
   <si>
+    <t>Serie anual OCDE TiVA SUT 2014-2021 para Marruecos (VA/P = 23.2%).</t>
+  </si>
+  <si>
+    <t>Producción minera vendible de roca fosfórica (revisado).</t>
+  </si>
+  <si>
     <t>Plantilla directa propia previa al programa de retiros voluntarios.</t>
   </si>
   <si>
+    <t>Producción minera vendible de roca fosfórica (cifra revisada en MCS 2026).</t>
+  </si>
+  <si>
     <t>OCP SA - Document de Référence (Enreg. AMMC EN/EM/031/2023)</t>
   </si>
   <si>
     <t>https://www.ammc.ma/en/espace-emetteurs/documents-enregistres/ocp-sa-ammc-registers-reference-document-financial-year-2022</t>
   </si>
   <si>
-    <t>Producción minera vendible de roca fosfórica (revisado).</t>
-  </si>
-  <si>
-    <t>Producción minera vendible de roca fosfórica (cifra revisada en MCS 2026).</t>
-  </si>
-  <si>
     <t>Estimación oficial de producción minera reportada en MCS 2026.</t>
   </si>
   <si>
@@ -380,105 +567,105 @@
     <t>HCP - Enquête Nationale sur l'Emploi</t>
   </si>
   <si>
+    <t>https://www.hcp.ma/Situation-du-marche-du-travail-en-2024_a4059.html</t>
+  </si>
+  <si>
     <t>Desglose: 9.990 operarios (OE), 5.830 técnicos (TAMCA), 2.537 ingenieros/cuadros (IC).</t>
   </si>
   <si>
-    <t>https://www.hcp.ma/Situation-du-marche-du-travail-en-2024_a4059.html</t>
+    <t>En las notas públicas de la encuesta de empleo, el HCP solo desagrega en 4 ramas agregadas (Agricultura, Industria, BTP, Servicios). La serie de "Mines et carrières" no se publica de forma desagregada y abierta en la web.</t>
+  </si>
+  <si>
+    <t>Producción de vehículos de motor</t>
+  </si>
+  <si>
+    <t>Unidades</t>
+  </si>
+  <si>
+    <t>OICA (Production Statistics)</t>
   </si>
   <si>
     <t>https://www.ammc.ma/en/espace-emetteurs/operations-financieres/ocp-sa-ammc-approves-information-dossier-relating</t>
   </si>
   <si>
-    <t>En las notas públicas de la encuesta de empleo, el HCP solo desagrega en 4 ramas agregadas (Agricultura, Industria, BTP, Servicios). La serie de "Mines et carrières" no se publica de forma desagregada y abierta en la web.</t>
-  </si>
-  <si>
-    <t>Producción de vehículos de motor</t>
-  </si>
-  <si>
-    <t>Unidades</t>
-  </si>
-  <si>
-    <t>OICA (Production Statistics)</t>
-  </si>
-  <si>
     <t>https://oica.net/wp-content/uploads/2025/11/prod-total-2025.pdf</t>
   </si>
   <si>
+    <t>Producción total de vehículos en Marruecos (fuente primaria OICA: CCFA).</t>
+  </si>
+  <si>
     <t>Desglose: 8.486 operarios (OE), 7.023 técnicos (TAMCA), 2.452 ingenieros/cuadros (IC).</t>
   </si>
   <si>
-    <t>Producción total de vehículos en Marruecos (fuente primaria OICA: CCFA).</t>
+    <t>Producción total de vehículos en Marruecos.</t>
+  </si>
+  <si>
+    <t>Producción total de vehículos en Marruecos (+15% interanual).</t>
   </si>
   <si>
     <t>Desglose: 7.547 operarios (OE), 7.650 técnicos (TAMCA), 2.491 ingenieros/cuadros (IC).</t>
   </si>
   <si>
-    <t>Producción total de vehículos en Marruecos.</t>
-  </si>
-  <si>
     <t>OCP SA - Document de Référence (Enreg. AMMC EN/EM/015/2024)</t>
   </si>
   <si>
     <t>https://www.ammc.ma/en/espace-emetteurs/liste-des-emetteurs/13927</t>
   </si>
   <si>
-    <t>Producción total de vehículos en Marruecos (+15% interanual).</t>
-  </si>
-  <si>
     <t>Producción total de vehículos en Marruecos (+4% interanual).</t>
   </si>
   <si>
     <t>Producción total de vehículos en Marruecos (-10% interanual).</t>
   </si>
   <si>
+    <t>Empleo automotor, serie anual</t>
+  </si>
+  <si>
+    <t>2c</t>
+  </si>
+  <si>
+    <t>Precio internacional DAP (f.o.b. US Gulf)</t>
+  </si>
+  <si>
+    <t>USD / tonelada métrica ($/mt)</t>
+  </si>
+  <si>
     <t>Plantilla directa en minas y química (~20.000 consolidada con filiales y servicios).</t>
   </si>
   <si>
-    <t>Empleo automotor, serie anual</t>
+    <t>World Bank Commodity Markets ("Pink Sheet")</t>
+  </si>
+  <si>
+    <t>https://thedocs.worldbank.org/en/doc/5d903e848db1d1b83e0ec8f744e55570-0350012021/related/CMO-Pink-Sheet-January-2025.pdf</t>
   </si>
   <si>
     <t>OCP Group - Résultats Annuels 2024 / AMMC</t>
   </si>
   <si>
-    <t>2c</t>
-  </si>
-  <si>
-    <t>Precio internacional DAP (f.o.b. US Gulf)</t>
-  </si>
-  <si>
-    <t>USD / tonelada métrica ($/mt)</t>
-  </si>
-  <si>
-    <t>World Bank Commodity Markets ("Pink Sheet")</t>
-  </si>
-  <si>
-    <t>https://thedocs.worldbank.org/en/doc/5d903e848db1d1b83e0ec8f744e55570-0350012021/related/CMO-Pink-Sheet-January-2025.pdf</t>
-  </si>
-  <si>
     <t>Promedio anual. Pico de precios por shock bélico e interrupción de suministros.</t>
   </si>
   <si>
+    <t>Promedio anual.</t>
+  </si>
+  <si>
     <t>Plantilla operativa consolidada en Marruecos vinculada al Green Investment Programme.</t>
   </si>
   <si>
-    <t>Promedio anual.</t>
-  </si>
-  <si>
     <t>OCP SA</t>
   </si>
   <si>
+    <t>Precio internacional roca fosfórica (f.o.b. North Africa)</t>
+  </si>
+  <si>
     <t>Ejercicio social 2025 no cerrado / pendiente de auditoría y reporte anual AMMC.</t>
   </si>
   <si>
-    <t>Precio internacional roca fosfórica (f.o.b. North Africa)</t>
+    <t>Promedio anual roca fosfórica Marruecos/África del Norte.</t>
   </si>
   <si>
     <t>Empleo total sector automotor</t>
   </si>
   <si>
-    <t>Promedio anual roca fosfórica Marruecos/África del Norte.</t>
-  </si>
-  <si>
     <t>Puestos de trabajo directos</t>
   </si>
   <si>
@@ -497,9 +684,6 @@
     <t>Pico histórico por guerra en Ucrania. Insumo crítico de amoníaco para la síntesis de fertilizantes fosfatados.</t>
   </si>
   <si>
-    <t>2d</t>
-  </si>
-  <si>
     <t>Salario real por sector (minería, automotor, agricultura)</t>
   </si>
   <si>
@@ -539,18 +723,18 @@
     <t>Bloque 4 - Síntesis y política</t>
   </si>
   <si>
+    <t>Carga global de compensación (Caisse de Compensation)</t>
+  </si>
+  <si>
+    <t>Ministère de l'Économie et des Finances - Rapport sur la compensation</t>
+  </si>
+  <si>
+    <t>https://www.finances.gov.ma/Publication/db/2024/Syntheserapportcompensation2024_FR.pdf</t>
+  </si>
+  <si>
     <t>Preservación de plantilla industrial durante Covid-19 y puesta en marcha de Stellantis Kenitra.</t>
   </si>
   <si>
-    <t>Carga global de compensación (Caisse de Compensation)</t>
-  </si>
-  <si>
-    <t>Ministère de l'Économie et des Finances - Rapport sur la compensation</t>
-  </si>
-  <si>
-    <t>https://www.finances.gov.ma/Publication/db/2024/Syntheserapportcompensation2024_FR.pdf</t>
-  </si>
-  <si>
     <t>Chef du Gouvernement / AHK Marokko Sectoral Report</t>
   </si>
   <si>
@@ -560,40 +744,43 @@
     <t>Gasto extraordinario para subsidiar gas butano (21.8 MMDH), trigo y azúcar, financiado en parte con rentas extraordinarias e impuestos de OCP.</t>
   </si>
   <si>
+    <t>Continuación del subsidio con relajación parcial de precios internacionales.</t>
+  </si>
+  <si>
+    <t>Carga global de compensación presupuestada</t>
+  </si>
+  <si>
+    <t>Ministère de l'Économie et des Finances - Loi de Finances 2024</t>
+  </si>
+  <si>
+    <t>Envolvente presupuestada en el proyecto de Ley de Finanzas 2024 para sostén de precios internos.</t>
+  </si>
+  <si>
+    <t>Régimen de zonas francas e incentivos fiscales a la inversión automotriz</t>
+  </si>
+  <si>
+    <t>Exoneración IS 5 años + 15% posterior; primas hasta 30%</t>
+  </si>
+  <si>
+    <t>Régimen legal / incentivos</t>
+  </si>
+  <si>
+    <t>AMDIE - Charte de l'Investissement &amp; Zones Économiques</t>
+  </si>
+  <si>
+    <t>https://www.amdie.gov.ma/charte-de-linvestissement/</t>
+  </si>
+  <si>
     <t>Rebote post-pandemia y ampliación del ecosistema de componentes.</t>
   </si>
   <si>
-    <t>Continuación del subsidio con relajación parcial de precios internacionales.</t>
-  </si>
-  <si>
     <t>Ministre de l'Industrie (Ryad Mezzour, Declaración parlamentaria)</t>
   </si>
   <si>
     <t>https://fr.le360.ma/economie/en-chiffres-la-strategie-automobile-du-maroc-expliquee-par-ryad-mezzour-270879/</t>
   </si>
   <si>
-    <t>Carga global de compensación presupuestada</t>
-  </si>
-  <si>
-    <t>Ministère de l'Économie et des Finances - Loi de Finances 2024</t>
-  </si>
-  <si>
-    <t>Envolvente presupuestada en el proyecto de Ley de Finanzas 2024 para sostén de precios internos.</t>
-  </si>
-  <si>
-    <t>Régimen de zonas francas e incentivos fiscales a la inversión automotriz</t>
-  </si>
-  <si>
-    <t>Exoneración IS 5 años + 15% posterior; primas hasta 30%</t>
-  </si>
-  <si>
-    <t>Régimen legal / incentivos</t>
-  </si>
-  <si>
-    <t>AMDIE - Charte de l'Investissement &amp; Zones Économiques</t>
-  </si>
-  <si>
-    <t>https://www.amdie.gov.ma/charte-de-linvestissement/</t>
+    <t>Marco de la Ley-marco 03-22 y Zones d'Accélération Industrielle (Tánger y Kenitra). Contraste: Estado subsidia capital externo para crear ventaja vs. ventaja natural en fosfatos.</t>
   </si>
   <si>
     <t>Declaración en sesión oral de la Cámara de Consejeros (22/11/2022).</t>
@@ -603,9 +790,6 @@
   </si>
   <si>
     <t>https://industries.ma/ayda-fathi-le-maroc-a-su-demontrer-sa-capacite-a-faire-face-aux-crises/</t>
-  </si>
-  <si>
-    <t>Marco de la Ley-marco 03-22 y Zones d'Accélération Industrielle (Tánger y Kenitra). Contraste: Estado subsidia capital externo para crear ventaja vs. ventaja natural en fosfatos.</t>
   </si>
   <si>
     <t>Confirmado en balance oficial sectorial (+220.000 a 230.000 empleos directos y estables).</t>
@@ -1148,6 +1332,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1426,28 +1614,28 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2">
         <v>5.0E7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
         <v>2024.0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4">
         <v>46281.0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1458,28 +1646,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2">
         <v>5.0E7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2">
         <v>2025.0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" s="4">
         <v>46281.0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -1490,28 +1678,28 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2">
         <v>84300.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2">
         <v>2021.0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="4">
         <v>46281.0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -1522,28 +1710,28 @@
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2">
         <v>114574.0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2">
         <v>2022.0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4">
         <v>46281.0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -1554,28 +1742,28 @@
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <v>91277.0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2">
         <v>2023.0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="4">
         <v>46281.0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -1586,28 +1774,28 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2">
         <v>97000.0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2">
         <v>2024.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I7" s="4">
         <v>46281.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -1618,28 +1806,28 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2">
         <v>36269.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2">
         <v>2021.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4">
         <v>46281.0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -1650,28 +1838,28 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2">
         <v>50076.0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2">
         <v>2022.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="4">
         <v>46281.0</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -1682,28 +1870,28 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2">
         <v>29396.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2">
         <v>2023.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="4">
         <v>46281.0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -1714,28 +1902,28 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2">
         <v>38800.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2">
         <v>2024.0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I11" s="4">
         <v>46281.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1746,28 +1934,28 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2">
         <v>13135.0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2">
         <v>2021.0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" s="4">
         <v>46281.0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1778,28 +1966,28 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2">
         <v>20011.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" s="2">
         <v>2022.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="4">
         <v>46281.0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -1810,28 +1998,28 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2">
         <v>26825.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2">
         <v>2023.0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" s="4">
         <v>46281.0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1842,28 +2030,28 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2">
         <v>20000.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2">
         <v>2023.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="4">
         <v>46281.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1874,28 +2062,28 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="F16" s="2">
         <v>2023.0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="I16" s="4">
         <v>46281.0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -1906,28 +2094,28 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2">
         <v>2023.0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="I17" s="4">
         <v>46281.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18">
@@ -1938,28 +2126,28 @@
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="F18" s="2">
         <v>2023.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="I18" s="4">
         <v>46281.0</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -1970,28 +2158,28 @@
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F19" s="2">
         <v>2023.0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="I19" s="4">
         <v>46281.0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -2002,28 +2190,28 @@
         <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D20" s="2">
         <v>-4.2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F20" s="2">
         <v>2023.0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I20" s="4">
         <v>46281.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21">
@@ -2034,28 +2222,28 @@
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D21" s="2">
         <v>11.5</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2">
         <v>2024.0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I21" s="4">
         <v>46281.0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -2066,28 +2254,28 @@
         <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D22" s="2">
         <v>7.5</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F22" s="2">
         <v>2025.0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I22" s="4">
         <v>46281.0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23">
@@ -2098,28 +2286,28 @@
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="D23" s="2">
         <v>3.2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F23" s="2">
         <v>2023.0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I23" s="4">
         <v>46281.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24">
@@ -2130,28 +2318,28 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="D24" s="2">
         <v>2.1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F24" s="2">
         <v>2024.0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I24" s="4">
         <v>46281.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25">
@@ -2162,28 +2350,28 @@
         <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="D25" s="2">
         <v>1.9</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F25" s="2">
         <v>2025.0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I25" s="4">
         <v>46281.0</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26">
@@ -2194,28 +2382,28 @@
         <v>11</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D26" s="2">
         <v>1340158.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F26" s="2">
         <v>2023.0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I26" s="4">
         <v>46281.0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27">
@@ -2226,28 +2414,28 @@
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D27" s="2">
         <v>1440407.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27" s="2">
         <v>2024.0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I27" s="4">
         <v>46281.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28">
@@ -2258,28 +2446,28 @@
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D28" s="2">
         <v>1517747.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F28" s="2">
         <v>2025.0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="I28" s="4">
         <v>46281.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29">
@@ -2287,31 +2475,31 @@
         <v>10</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D29" s="2">
         <v>35200.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2">
         <v>2019.0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="I29" s="4">
         <v>46281.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30">
@@ -2319,31 +2507,31 @@
         <v>10</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D30" s="2">
         <v>37400.0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2">
         <v>2020.0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="I30" s="4">
         <v>46281.0</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31">
@@ -2351,31 +2539,31 @@
         <v>10</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D31" s="2">
         <v>38100.0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="2">
         <v>2021.0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="I31" s="4">
         <v>46281.0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
@@ -2383,31 +2571,31 @@
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D32" s="2">
         <v>38000.0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="2">
         <v>2022.0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="I32" s="4">
         <v>46281.0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33">
@@ -2415,31 +2603,31 @@
         <v>10</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D33" s="2">
         <v>33000.0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="2">
         <v>2023.0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="I33" s="4">
         <v>46281.0</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
@@ -2447,31 +2635,31 @@
         <v>10</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D34" s="2">
         <v>35300.0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="2">
         <v>2024.0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I34" s="4">
         <v>46281.0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35">
@@ -2479,31 +2667,31 @@
         <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D35" s="2">
         <v>36000.0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" s="2">
         <v>2025.0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I35" s="4">
         <v>46281.0</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
@@ -2511,31 +2699,31 @@
         <v>10</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="F36" s="2">
         <v>2023.0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>123</v>
+        <v>184</v>
       </c>
       <c r="I36" s="4">
         <v>46281.0</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37">
@@ -2543,31 +2731,31 @@
         <v>10</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D37" s="2">
         <v>403218.0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F37" s="2">
         <v>2019.0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="I37" s="4">
         <v>46281.0</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38">
@@ -2575,31 +2763,31 @@
         <v>10</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D38" s="2">
         <v>403007.0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F38" s="2">
         <v>2021.0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="I38" s="4">
         <v>46281.0</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39">
@@ -2607,31 +2795,31 @@
         <v>10</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D39" s="2">
         <v>464864.0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F39" s="2">
         <v>2022.0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="I39" s="4">
         <v>46281.0</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40">
@@ -2639,31 +2827,31 @@
         <v>10</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D40" s="2">
         <v>535825.0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F40" s="2">
         <v>2023.0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="I40" s="4">
         <v>46281.0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41">
@@ -2671,31 +2859,31 @@
         <v>10</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D41" s="2">
         <v>559645.0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F41" s="2">
         <v>2024.0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="I41" s="4">
         <v>46281.0</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42">
@@ -2703,31 +2891,31 @@
         <v>10</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D42" s="2">
         <v>501965.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F42" s="2">
         <v>2025.0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="I42" s="4">
         <v>46281.0</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43">
@@ -2735,31 +2923,31 @@
         <v>10</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="F43" s="2">
         <v>2023.0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="I43" s="4">
         <v>46281.0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44">
@@ -2767,31 +2955,31 @@
         <v>10</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="D44" s="2">
         <v>772.2</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="F44" s="2">
         <v>2022.0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I44" s="4">
         <v>46281.0</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45">
@@ -2799,31 +2987,31 @@
         <v>10</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="D45" s="2">
         <v>550.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="F45" s="2">
         <v>2023.0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I45" s="4">
         <v>46281.0</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46">
@@ -2831,31 +3019,31 @@
         <v>10</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="D46" s="2">
         <v>563.7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="F46" s="2">
         <v>2024.0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I46" s="4">
         <v>46281.0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47">
@@ -2863,31 +3051,31 @@
         <v>10</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
       <c r="D47" s="2">
         <v>266.2</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="F47" s="2">
         <v>2022.0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I47" s="4">
         <v>46281.0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>154</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48">
@@ -2895,31 +3083,31 @@
         <v>10</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
       <c r="D48" s="2">
         <v>323.8</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="F48" s="2">
         <v>2023.0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I48" s="4">
         <v>46281.0</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49">
@@ -2927,31 +3115,31 @@
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
       <c r="D49" s="2">
         <v>321.7</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="F49" s="2">
         <v>2024.0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I49" s="4">
         <v>46281.0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50">
@@ -2959,31 +3147,31 @@
         <v>10</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="D50" s="2">
         <v>40.34</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="F50" s="2">
         <v>2022.0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I50" s="4">
         <v>46281.0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51">
@@ -2991,31 +3179,31 @@
         <v>10</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="D51" s="2">
         <v>13.11</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="F51" s="2">
         <v>2023.0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I51" s="4">
         <v>46281.0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52">
@@ -3023,31 +3211,31 @@
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="D52" s="2">
         <v>12.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="F52" s="2">
         <v>2024.0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="I52" s="4">
         <v>46281.0</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53">
@@ -3055,31 +3243,31 @@
         <v>10</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="F53" s="2">
         <v>2023.0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="I53" s="4">
         <v>46281.0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>168</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54">
@@ -3087,31 +3275,31 @@
         <v>10</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="D54" s="2">
         <v>5126.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F54" s="2">
         <v>2021.0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I54" s="4">
         <v>46281.0</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55">
@@ -3119,31 +3307,31 @@
         <v>10</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="D55" s="2">
         <v>8163.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F55" s="2">
         <v>2022.0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I55" s="4">
         <v>46281.0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56">
@@ -3151,159 +3339,159 @@
         <v>10</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="D56" s="2">
         <v>7251.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F56" s="2">
         <v>2023.0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I56" s="4">
         <v>46281.0</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B57" s="2">
         <v>4.0</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D57" s="2">
         <v>42060.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F57" s="2">
         <v>2022.0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="I57" s="4">
         <v>46281.0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B58" s="2">
         <v>4.0</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D58" s="2">
         <v>30000.0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F58" s="2">
         <v>2023.0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="I58" s="4">
         <v>46281.0</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B59" s="2">
         <v>4.0</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="D59" s="2">
         <v>16357.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F59" s="2">
         <v>2024.0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="I59" s="4">
         <v>46281.0</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B60" s="2">
         <v>4.0</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>189</v>
+        <v>247</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="F60" s="2">
         <v>2023.0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>192</v>
+        <v>250</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="I60" s="4">
         <v>46281.0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>197</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -3384,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>2</v>
@@ -3413,290 +3601,290 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6">
         <v>2014.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I2" s="8">
         <v>46281.0</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F3" s="6">
         <v>2014.0</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I3" s="8">
         <v>46281.0</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="F4" s="6">
         <v>2014.0</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I4" s="8">
         <v>46281.0</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="F5" s="6">
         <v>2014.0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8">
         <v>46281.0</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F6" s="6">
         <v>2014.0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I6" s="8">
         <v>46281.0</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F7" s="6">
         <v>2014.0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I7" s="8">
         <v>46281.0</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D8" s="9">
         <v>0.635</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F8" s="6">
         <v>2024.0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="I8" s="8">
         <v>46281.0</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="D9" s="9">
         <v>0.338</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F9" s="6">
         <v>2024.0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="I9" s="8">
         <v>46281.0</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="F10" s="6">
         <v>2024.0</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="I10" s="8">
         <v>46281.0</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -3704,31 +3892,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D11" s="6">
         <v>20000.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F11" s="6">
         <v>2019.0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" s="8">
         <v>46281.0</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -3736,31 +3924,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D12" s="6">
         <v>18357.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F12" s="6">
         <v>2020.0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I12" s="8">
         <v>46281.0</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13">
@@ -3768,31 +3956,31 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D13" s="6">
         <v>17961.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F13" s="6">
         <v>2021.0</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="I13" s="8">
         <v>46281.0</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14">
@@ -3800,31 +3988,31 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D14" s="6">
         <v>17688.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F14" s="6">
         <v>2022.0</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I14" s="8">
         <v>46281.0</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
@@ -3832,31 +4020,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D15" s="6">
         <v>17000.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F15" s="6">
         <v>2023.0</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="I15" s="8">
         <v>46281.0</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">
@@ -3864,31 +4052,31 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D16" s="6">
         <v>20000.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F16" s="6">
         <v>2024.0</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I16" s="8">
         <v>46281.0</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
@@ -3896,31 +4084,31 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F17" s="6">
         <v>2025.0</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="I17" s="8">
         <v>46281.0</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
@@ -3928,31 +4116,31 @@
         <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D18" s="6">
         <v>148000.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F18" s="6">
         <v>2019.0</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="I18" s="8">
         <v>46281.0</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>165</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
@@ -3960,31 +4148,31 @@
         <v>10</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D19" s="6">
         <v>160000.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F19" s="6">
         <v>2020.0</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>167</v>
+        <v>228</v>
       </c>
       <c r="I19" s="8">
         <v>46281.0</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>175</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20">
@@ -3992,31 +4180,31 @@
         <v>10</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D20" s="6">
         <v>180000.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F20" s="6">
         <v>2021.0</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I20" s="8">
         <v>46281.0</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21">
@@ -4024,31 +4212,31 @@
         <v>10</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D21" s="6">
         <v>220000.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F21" s="6">
         <v>2022.0</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="I21" s="8">
         <v>46281.0</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22">
@@ -4056,31 +4244,31 @@
         <v>10</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D22" s="6">
         <v>230000.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F22" s="6">
         <v>2023.0</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="I22" s="8">
         <v>46281.0</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23">
@@ -4088,31 +4276,31 @@
         <v>10</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D23" s="6">
         <v>238000.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F23" s="6">
         <v>2024.0</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I23" s="8">
         <v>46281.0</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24">
@@ -4120,31 +4308,31 @@
         <v>10</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="D24" s="6">
         <v>250000.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="F24" s="6">
         <v>2025.0</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>202</v>
+        <v>263</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="I24" s="8">
         <v>46281.0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25">
@@ -4152,31 +4340,31 @@
         <v>10</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D25" s="6">
         <v>77128.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F25" s="6">
         <v>2019.0</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="I25" s="8">
         <v>46281.0</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26">
@@ -4184,31 +4372,31 @@
         <v>10</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D26" s="6">
         <v>72283.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F26" s="6">
         <v>2020.0</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="I26" s="8">
         <v>46281.0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27">
@@ -4216,31 +4404,31 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D27" s="6">
         <v>83783.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27" s="6">
         <v>2021.0</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="I27" s="8">
         <v>46281.0</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28">
@@ -4248,31 +4436,31 @@
         <v>10</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D28" s="6">
         <v>111281.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F28" s="6">
         <v>2022.0</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I28" s="8">
         <v>46281.0</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29">
@@ -4280,31 +4468,31 @@
         <v>10</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D29" s="6">
         <v>141763.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29" s="6">
         <v>2023.0</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I29" s="8">
         <v>46281.0</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30">
@@ -4312,31 +4500,31 @@
         <v>10</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
       <c r="D30" s="6">
         <v>148000.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30" s="6">
         <v>2023.0</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="I30" s="8">
         <v>46281.0</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31">
@@ -4344,31 +4532,31 @@
         <v>10</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D31" s="6">
         <v>157594.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31" s="6">
         <v>2024.0</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I31" s="8">
         <v>46281.0</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32">
@@ -4376,31 +4564,31 @@
         <v>10</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D32" s="6">
         <v>154494.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F32" s="6">
         <v>2025.0</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I32" s="8">
         <v>46281.0</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33">
@@ -4408,31 +4596,31 @@
         <v>10</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D33" s="6">
         <v>33500.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33" s="6">
         <v>2019.0</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="I33" s="8">
         <v>46281.0</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34">
@@ -4440,31 +4628,31 @@
         <v>10</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D34" s="6">
         <v>25695.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F34" s="6">
         <v>2020.0</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="I34" s="8">
         <v>46281.0</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35">
@@ -4472,31 +4660,31 @@
         <v>10</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D35" s="6">
         <v>25206.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F35" s="6">
         <v>2021.0</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="I35" s="8">
         <v>46281.0</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36">
@@ -4504,31 +4692,31 @@
         <v>10</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D36" s="6">
         <v>34810.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36" s="6">
         <v>2022.0</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I36" s="8">
         <v>46281.0</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37">
@@ -4536,31 +4724,31 @@
         <v>10</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D37" s="6">
         <v>46136.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F37" s="6">
         <v>2023.0</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I37" s="8">
         <v>46281.0</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38">
@@ -4568,31 +4756,31 @@
         <v>10</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D38" s="6">
         <v>53643.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F38" s="6">
         <v>2024.0</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I38" s="8">
         <v>46281.0</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39">
@@ -4600,31 +4788,31 @@
         <v>10</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="D39" s="6">
         <v>57777.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F39" s="6">
         <v>2025.0</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I39" s="8">
         <v>46281.0</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40">
@@ -4632,31 +4820,31 @@
         <v>10</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D40" s="6">
         <v>34000.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="6">
         <v>2019.0</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="I40" s="8">
         <v>46281.0</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41">
@@ -4664,31 +4852,31 @@
         <v>10</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D41" s="6">
         <v>29216.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" s="6">
         <v>2020.0</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="I41" s="8">
         <v>46281.0</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42">
@@ -4696,31 +4884,31 @@
         <v>10</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D42" s="6">
         <v>39491.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F42" s="6">
         <v>2021.0</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="I42" s="8">
         <v>46281.0</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43">
@@ -4728,31 +4916,31 @@
         <v>10</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D43" s="6">
         <v>55149.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F43" s="6">
         <v>2022.0</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I43" s="8">
         <v>46281.0</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44">
@@ -4760,31 +4948,31 @@
         <v>10</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D44" s="6">
         <v>67629.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F44" s="6">
         <v>2023.0</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I44" s="8">
         <v>46281.0</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45">
@@ -4792,31 +4980,31 @@
         <v>10</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D45" s="6">
         <v>70955.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" s="6">
         <v>2024.0</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I45" s="8">
         <v>46281.0</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46">
@@ -4824,31 +5012,31 @@
         <v>10</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D46" s="6">
         <v>61299.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F46" s="6">
         <v>2025.0</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I46" s="8">
         <v>46281.0</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47">
@@ -4856,31 +5044,31 @@
         <v>10</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D47" s="6">
         <v>48923.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F47" s="6">
         <v>2019.0</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="I47" s="8">
         <v>46281.0</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>241</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48">
@@ -4888,31 +5076,31 @@
         <v>10</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D48" s="6">
         <v>50869.0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48" s="6">
         <v>2020.0</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="I48" s="8">
         <v>46281.0</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>242</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49">
@@ -4920,31 +5108,31 @@
         <v>10</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D49" s="6">
         <v>79893.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F49" s="6">
         <v>2021.0</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="I49" s="8">
         <v>46281.0</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>243</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50">
@@ -4952,31 +5140,31 @@
         <v>10</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D50" s="6">
         <v>115484.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F50" s="6">
         <v>2022.0</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I50" s="8">
         <v>46281.0</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>244</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51">
@@ -4984,31 +5172,31 @@
         <v>10</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D51" s="6">
         <v>76141.0</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51" s="6">
         <v>2023.0</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="I51" s="8">
         <v>46281.0</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
     </row>
     <row r="52">
@@ -5016,31 +5204,31 @@
         <v>10</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D52" s="6">
         <v>87083.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F52" s="6">
         <v>2024.0</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I52" s="8">
         <v>46281.0</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>246</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53">
@@ -5048,31 +5236,31 @@
         <v>10</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="D53" s="6">
         <v>99804.0</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F53" s="6">
         <v>2025.0</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="I53" s="8">
         <v>46281.0</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54">
@@ -5083,28 +5271,28 @@
         <v>11</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="D54" s="6">
         <v>14000.0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F54" s="6">
         <v>2022.0</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="I54" s="8">
         <v>46281.0</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>251</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55">
@@ -5115,28 +5303,28 @@
         <v>11</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>252</v>
+        <v>313</v>
       </c>
       <c r="D55" s="6">
         <v>9000.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F55" s="6">
         <v>2022.0</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="I55" s="8">
         <v>46281.0</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56">
@@ -5147,28 +5335,28 @@
         <v>11</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="D56" s="6">
         <v>20000.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F56" s="6">
         <v>2024.0</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="I56" s="8">
         <v>46281.0</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57">
@@ -5179,28 +5367,28 @@
         <v>11</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="D57" s="6">
         <v>152000.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F57" s="6">
         <v>2020.0</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="I57" s="8">
         <v>46281.0</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>261</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58">
@@ -5211,28 +5399,28 @@
         <v>11</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="F58" s="6">
         <v>2022.0</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="I58" s="8">
         <v>46281.0</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>267</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59">
@@ -5240,31 +5428,31 @@
         <v>10</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="D59" s="6">
         <v>5255.0</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F59" s="6">
         <v>2019.0</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="I59" s="8">
         <v>46281.0</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60">
@@ -5272,31 +5460,31 @@
         <v>10</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="D60" s="6">
         <v>5500.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F60" s="6">
         <v>2023.0</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="I60" s="8">
         <v>46281.0</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>275</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61">
@@ -5304,31 +5492,31 @@
         <v>10</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="D61" s="6">
         <v>5871.0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F61" s="6">
         <v>2024.0</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="I61" s="8">
         <v>46281.0</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62">
@@ -5336,31 +5524,31 @@
         <v>10</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>277</v>
+        <v>338</v>
       </c>
       <c r="D62" s="6">
         <v>5002.0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F62" s="6">
         <v>2020.0</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="I62" s="8">
         <v>46281.0</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63">
@@ -5368,31 +5556,31 @@
         <v>10</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="D63" s="6">
         <v>2975.0</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F63" s="6">
         <v>2020.0</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="I63" s="8">
         <v>46281.0</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64">
@@ -5400,31 +5588,31 @@
         <v>10</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="D64" s="6">
         <v>6520.0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F64" s="6">
         <v>2020.0</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="I64" s="8">
         <v>46281.0</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
     </row>
     <row r="65">
@@ -5432,31 +5620,31 @@
         <v>10</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="D65" s="6">
         <v>14937.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F65" s="6">
         <v>2020.0</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="I65" s="8">
         <v>46281.0</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66">
@@ -5464,383 +5652,383 @@
         <v>10</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="F66" s="6">
         <v>2024.0</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>287</v>
+        <v>348</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="I66" s="8">
         <v>46281.0</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>288</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D67" s="6">
         <v>66500.0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F67" s="6">
         <v>2019.0</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="I67" s="8">
         <v>46281.0</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>294</v>
+        <v>355</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D68" s="6">
         <v>67500.0</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F68" s="6">
         <v>2020.0</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="I68" s="8">
         <v>46281.0</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>297</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D69" s="6">
         <v>72994.0</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F69" s="6">
         <v>2021.0</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>298</v>
+        <v>359</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>299</v>
+        <v>360</v>
       </c>
       <c r="I69" s="8">
         <v>46281.0</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D70" s="6">
         <v>63278.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F70" s="6">
         <v>2022.0</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="I70" s="8">
         <v>46281.0</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D71" s="6">
         <v>69297.0</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F71" s="6">
         <v>2023.0</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="I71" s="8">
         <v>46281.0</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>304</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D72" s="6">
         <v>71500.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F72" s="6">
         <v>2024.0</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="I72" s="8">
         <v>46281.0</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="D73" s="6">
         <v>194400.0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F73" s="6">
         <v>2020.0</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>310</v>
+        <v>371</v>
       </c>
       <c r="I73" s="8">
         <v>46281.0</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>311</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="D74" s="6">
         <v>132400.0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F74" s="6">
         <v>2020.0</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>313</v>
+        <v>374</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="I74" s="8">
         <v>46281.0</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="D75" s="6">
         <v>53100.0</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F75" s="6">
         <v>2020.0</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="I75" s="8">
         <v>46281.0</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>319</v>
+        <v>380</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>320</v>
+        <v>381</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F76" s="6">
         <v>2020.0</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="I76" s="8">
         <v>46281.0</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>322</v>
+        <v>383</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F77" s="6">
         <v>2020.0</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="I77" s="8">
         <v>46281.0</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>324</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5927,4 +6115,986 @@
     <tablePart r:id="rId79"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="31.63"/>
+    <col customWidth="1" min="2" max="2" width="5.25"/>
+    <col customWidth="1" min="3" max="3" width="54.38"/>
+    <col customWidth="1" min="4" max="4" width="14.25"/>
+    <col customWidth="1" min="5" max="5" width="18.75"/>
+    <col customWidth="1" min="6" max="6" width="4.63"/>
+    <col customWidth="1" min="7" max="7" width="46.13"/>
+    <col customWidth="1" min="8" max="8" width="87.5"/>
+    <col customWidth="1" min="9" max="9" width="14.25"/>
+    <col customWidth="1" min="10" max="10" width="129.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10550.0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2">
+        <v>11615.0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2">
+        <v>11518.0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2">
+        <v>587384.0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2">
+        <v>656660.0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2">
+        <v>677529.0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="2">
+        <v>580750.0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2">
+        <v>575900.0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="2">
+        <v>51423.0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2">
+        <v>74053.0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2">
+        <v>60852.0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="2">
+        <v>18546.0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="2">
+        <v>23232.0</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="2">
+        <v>13982.0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="2">
+        <v>11802.0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="2">
+        <v>13447.0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="2">
+        <v>11530.0</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2529.0</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3842.0</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4913.0</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="2">
+        <v>43.52</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2014.0</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I22" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2014.0</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2014.0</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I25" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I26" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="2">
+        <v>43.1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I28" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" s="2">
+        <v>76.8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I29" s="4">
+        <v>46283.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="H2"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="H4"/>
+    <hyperlink r:id="rId4" ref="H5"/>
+    <hyperlink r:id="rId5" ref="H6"/>
+    <hyperlink r:id="rId6" ref="H7"/>
+    <hyperlink r:id="rId7" ref="H8"/>
+    <hyperlink r:id="rId8" ref="H9"/>
+    <hyperlink r:id="rId9" ref="H10"/>
+    <hyperlink r:id="rId10" ref="H11"/>
+    <hyperlink r:id="rId11" ref="H12"/>
+    <hyperlink r:id="rId12" ref="H13"/>
+    <hyperlink r:id="rId13" ref="H14"/>
+    <hyperlink r:id="rId14" ref="H15"/>
+    <hyperlink r:id="rId15" ref="H16"/>
+    <hyperlink r:id="rId16" ref="H17"/>
+    <hyperlink r:id="rId17" ref="H18"/>
+    <hyperlink r:id="rId18" ref="H19"/>
+    <hyperlink r:id="rId19" ref="H20"/>
+    <hyperlink r:id="rId20" ref="H21"/>
+    <hyperlink r:id="rId21" ref="H22"/>
+    <hyperlink r:id="rId22" ref="H23"/>
+    <hyperlink r:id="rId23" ref="H24"/>
+    <hyperlink r:id="rId24" ref="H25"/>
+    <hyperlink r:id="rId25" ref="H26"/>
+    <hyperlink r:id="rId26" ref="H27"/>
+    <hyperlink r:id="rId27" ref="H28"/>
+    <hyperlink r:id="rId28" ref="H29"/>
+  </hyperlinks>
+  <drawing r:id="rId29"/>
+</worksheet>
 </file>